--- a/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_06-16-26.xlsx
+++ b/T41_V012_Files/T41_V012_BOMs/Source Files/T41_RF_Board_BOM_V012.8_06-16-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\T41\T41_V012_Files\T41_V012_BOMs\Source Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CF5D22-1ACB-4369-A9B8-6A7FEA863529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E9663F-5050-4639-9512-3882A2FDE613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,11 +3034,11 @@
         <v>285</v>
       </c>
       <c r="G53" s="5">
-        <v>5.24</v>
+        <v>5.84</v>
       </c>
       <c r="H53" s="5">
         <f t="shared" si="1"/>
-        <v>10.48</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -3056,11 +3056,11 @@
         <v>285</v>
       </c>
       <c r="G54" s="5">
-        <v>9.25</v>
+        <v>11.74</v>
       </c>
       <c r="H54" s="9">
         <f t="shared" si="1"/>
-        <v>9.25</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H55" s="10">
         <f>SUM(H2:H54)</f>
-        <v>88.917000000000016</v>
+        <v>92.607000000000014</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
@@ -3844,11 +3844,11 @@
         <v>285</v>
       </c>
       <c r="G35" s="5">
-        <v>5.24</v>
+        <v>5.84</v>
       </c>
       <c r="H35" s="5">
         <f t="shared" si="0"/>
-        <v>5.24</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -3866,11 +3866,11 @@
         <v>285</v>
       </c>
       <c r="G36" s="5">
-        <v>9.25</v>
+        <v>11.74</v>
       </c>
       <c r="H36" s="9">
         <f t="shared" si="0"/>
-        <v>9.25</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -3881,7 +3881,7 @@
       <c r="G37" s="1"/>
       <c r="H37" s="10">
         <f>SUM(H2:H36)</f>
-        <v>58.443000000000005</v>
+        <v>61.533000000000008</v>
       </c>
     </row>
   </sheetData>
